--- a/Excel/ZuoQiShowConfig.xlsx
+++ b/Excel/ZuoQiShowConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F3587E-59D2-49F2-9B3C-8350701AE331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1D10B6-82E5-4DFD-9034-77632618BC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZuoQiShowProto" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{27F8CE97-7D6F-43E5-9544-4E835CD61823}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{27F8CE97-7D6F-43E5-9544-4E835CD61823}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
   <si>
     <t>ID</t>
   </si>
@@ -253,6 +253,115 @@
   </si>
   <si>
     <t>精灵羊驼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Charge Wild Boar</t>
+  </si>
+  <si>
+    <t>Gladiator Goat</t>
+  </si>
+  <si>
+    <t>Dulcere</t>
+  </si>
+  <si>
+    <t>Jieying</t>
+  </si>
+  <si>
+    <t>Spring of the Deer</t>
+  </si>
+  <si>
+    <t>Guardian Yak</t>
+  </si>
+  <si>
+    <t>Flame Dragon</t>
+  </si>
+  <si>
+    <t>Savage Hunter</t>
+  </si>
+  <si>
+    <t>Ghost Void Dragon</t>
+  </si>
+  <si>
+    <t>Arctic Giant Bear</t>
+  </si>
+  <si>
+    <t>Elf Alpaca</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Damage dealt increases by 2%</t>
+  </si>
+  <si>
+    <t>Life cap + 1%</t>
+  </si>
+  <si>
+    <t>Game drop rate +5%</t>
+  </si>
+  <si>
+    <t>Critical hit rate + 2%</t>
+  </si>
+  <si>
+    <t>Heavy Strike probability +3%</t>
+  </si>
+  <si>
+    <t>Attack increases by 5% and damage to monsters increases by 10%</t>
+  </si>
+  <si>
+    <t>Attack increases by 1%</t>
+  </si>
+  <si>
+    <t>Damage increase by 5% and damage to monsters increased by 10%</t>
+  </si>
+  <si>
+    <t>Attack power increases by 5%</t>
+  </si>
+  <si>
+    <t>Obtained by completing the mount quest at level 25 (rewards for Bounty Hunters)</t>
+  </si>
+  <si>
+    <t>Obtained through the in-game accumulation system</t>
+  </si>
+  <si>
+    <t>Obtained through the in-game achievement system.</t>
+  </si>
+  <si>
+    <t>The game's ranking will automatically activate (3 days later)</t>
+  </si>
+  <si>
+    <t>Obtain through the Explorer Points in the game</t>
+  </si>
+  <si>
+    <t>Obtained by exchanging the mount rope in the game</t>
+  </si>
+  <si>
+    <t>Obtained through the in-game token system</t>
+  </si>
+  <si>
+    <t>Obtained by ranking first in the game's arena</t>
+  </si>
+  <si>
+    <t>Obtained through exchanging with Divine Beast Fragments</t>
+  </si>
+  <si>
+    <t>Des_EN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetDes_EN</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -645,27 +754,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:M20"/>
+  <dimension ref="C1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="16.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="28.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="30.875" style="2" customWidth="1"/>
+    <col min="13" max="14" width="25.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.875" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -673,34 +793,43 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
@@ -708,34 +837,43 @@
         <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
@@ -743,10 +881,10 @@
         <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>21</v>
@@ -764,432 +902,549 @@
         <v>21</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="3:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>10001</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="1">
         <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10001</v>
       </c>
       <c r="G6" s="1">
         <v>10001</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
+        <v>10001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O6" s="1">
         <v>99001001</v>
       </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>10002</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="1">
         <v>2</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10002</v>
       </c>
       <c r="G7" s="1">
         <v>10002</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
+        <v>10002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="1">
         <v>99001005</v>
       </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>10003</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="1">
         <v>3</v>
-      </c>
-      <c r="F8" s="1">
-        <v>10003</v>
       </c>
       <c r="G8" s="1">
         <v>10003</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
+        <v>10003</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" s="1">
         <v>99001001</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>10004</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="1">
         <v>4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10004</v>
       </c>
       <c r="G9" s="1">
         <v>10004</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="s">
+        <v>10004</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="1">
         <v>99001003</v>
       </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>10005</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="1">
         <v>4</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10005</v>
       </c>
       <c r="G10" s="1">
         <v>10005</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="s">
+        <v>10005</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="1">
         <v>99001002</v>
       </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>10006</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="1">
         <v>4</v>
-      </c>
-      <c r="F11" s="1">
-        <v>10006</v>
       </c>
       <c r="G11" s="1">
         <v>10006</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1" t="s">
+        <v>10006</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="1">
         <v>99001002</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="1">
         <v>10007</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="1">
         <v>4</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10007</v>
       </c>
       <c r="G12" s="1">
         <v>10007</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="s">
+        <v>10007</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" s="1">
         <v>99001002</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="1">
         <v>10008</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="1">
         <v>5</v>
-      </c>
-      <c r="F13" s="1">
-        <v>10008</v>
       </c>
       <c r="G13" s="1">
         <v>10008</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="s">
+        <v>10008</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" t="s">
+        <v>91</v>
+      </c>
+      <c r="O13" s="1">
         <v>99001003</v>
       </c>
-      <c r="M13" s="1">
+      <c r="P13" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1">
         <v>10009</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="1">
         <v>4</v>
-      </c>
-      <c r="F14" s="1">
-        <v>10009</v>
       </c>
       <c r="G14" s="1">
         <v>10009</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
+        <v>10009</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L14" s="1">
+      <c r="N14" t="s">
+        <v>94</v>
+      </c>
+      <c r="O14" s="1">
         <v>99001002</v>
       </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="1">
         <v>10010</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1">
         <v>5</v>
-      </c>
-      <c r="F15" s="1">
-        <v>10010</v>
       </c>
       <c r="G15" s="1">
         <v>10010</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
+        <v>10010</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" t="s">
+        <v>91</v>
+      </c>
+      <c r="O15" s="1">
         <v>99001004</v>
       </c>
-      <c r="M15" s="1">
+      <c r="P15" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="1">
         <v>10011</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="1">
         <v>5</v>
-      </c>
-      <c r="F16" s="1">
-        <v>10011</v>
       </c>
       <c r="G16" s="1">
         <v>10011</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
+        <v>10011</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N16" t="s">
+        <v>91</v>
+      </c>
+      <c r="O16" s="1">
         <v>99001002</v>
       </c>
-      <c r="M16" s="1">
+      <c r="P16" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="1">
         <v>10012</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="1">
         <v>5</v>
-      </c>
-      <c r="F17" s="1">
-        <v>10012</v>
       </c>
       <c r="G17" s="1">
         <v>10012</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
+        <v>10012</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" t="s">
+        <v>86</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O17" s="1">
         <v>99001003</v>
       </c>
-      <c r="M17" s="1">
+      <c r="P17" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/ZuoQiShowConfig.xlsx
+++ b/Excel/ZuoQiShowConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1D10B6-82E5-4DFD-9034-77632618BC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8CD93A-3E03-4C53-9AFA-2D18AA5D5636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,39 +259,12 @@
     <t>Horse</t>
   </si>
   <si>
-    <t>Charge Wild Boar</t>
-  </si>
-  <si>
     <t>Gladiator Goat</t>
   </si>
   <si>
-    <t>Dulcere</t>
-  </si>
-  <si>
-    <t>Jieying</t>
-  </si>
-  <si>
-    <t>Spring of the Deer</t>
-  </si>
-  <si>
     <t>Guardian Yak</t>
   </si>
   <si>
-    <t>Flame Dragon</t>
-  </si>
-  <si>
-    <t>Savage Hunter</t>
-  </si>
-  <si>
-    <t>Ghost Void Dragon</t>
-  </si>
-  <si>
-    <t>Arctic Giant Bear</t>
-  </si>
-  <si>
-    <t>Elf Alpaca</t>
-  </si>
-  <si>
     <t>Name_EN</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -362,6 +335,36 @@
   </si>
   <si>
     <t>GetDes_EN</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charging Boar</t>
+  </si>
+  <si>
+    <t>Spring Elk</t>
+  </si>
+  <si>
+    <t>Lava Dragon</t>
+  </si>
+  <si>
+    <t>Arena Ape</t>
+  </si>
+  <si>
+    <t>Arctic Grizzly</t>
+  </si>
+  <si>
+    <t>Elven Alpaca</t>
+  </si>
+  <si>
+    <t>Dilu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jueying</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghost Dragon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -369,7 +372,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,6 +417,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -441,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -450,6 +461,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -754,13 +766,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:P20"/>
+  <dimension ref="B1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="8" width="28.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="16.875" style="2" customWidth="1"/>
@@ -773,19 +786,19 @@
     <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -829,7 +842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
@@ -837,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -855,7 +868,7 @@
         <v>15</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>16</v>
@@ -864,7 +877,7 @@
         <v>17</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>18</v>
@@ -873,7 +886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
@@ -917,7 +930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>10001</v>
       </c>
@@ -942,14 +955,14 @@
       <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K6" t="s">
-        <v>77</v>
+      <c r="K6" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="O6" s="1">
         <v>99001001</v>
@@ -958,7 +971,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
       <c r="C7" s="1">
         <v>10002</v>
       </c>
@@ -966,7 +980,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -983,8 +997,8 @@
       <c r="J7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K7" t="s">
-        <v>78</v>
+      <c r="K7" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>28</v>
@@ -993,7 +1007,7 @@
         <v>29</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O7" s="1">
         <v>99001005</v>
@@ -1002,7 +1016,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1"/>
       <c r="C8" s="1">
         <v>10003</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="1">
         <v>3</v>
@@ -1027,8 +1042,8 @@
       <c r="J8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K8" t="s">
-        <v>79</v>
+      <c r="K8" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>32</v>
@@ -1037,7 +1052,7 @@
         <v>33</v>
       </c>
       <c r="N8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O8" s="1">
         <v>99001001</v>
@@ -1046,7 +1061,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
       <c r="C9" s="1">
         <v>10004</v>
       </c>
@@ -1054,7 +1070,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -1071,8 +1087,8 @@
       <c r="J9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K9" t="s">
-        <v>80</v>
+      <c r="K9" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>36</v>
@@ -1081,7 +1097,7 @@
         <v>37</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O9" s="1">
         <v>99001003</v>
@@ -1090,7 +1106,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
       <c r="C10" s="1">
         <v>10005</v>
       </c>
@@ -1098,7 +1115,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -1115,8 +1132,8 @@
       <c r="J10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K10" t="s">
-        <v>81</v>
+      <c r="K10" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>40</v>
@@ -1125,7 +1142,7 @@
         <v>41</v>
       </c>
       <c r="N10" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O10" s="1">
         <v>99001002</v>
@@ -1134,7 +1151,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>10006</v>
       </c>
@@ -1142,7 +1160,7 @@
         <v>42</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
@@ -1159,8 +1177,8 @@
       <c r="J11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K11" t="s">
-        <v>81</v>
+      <c r="K11" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>40</v>
@@ -1169,7 +1187,7 @@
         <v>43</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O11" s="1">
         <v>99001002</v>
@@ -1178,7 +1196,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>10007</v>
       </c>
@@ -1186,7 +1205,7 @@
         <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -1203,8 +1222,8 @@
       <c r="J12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K12" t="s">
-        <v>82</v>
+      <c r="K12" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>46</v>
@@ -1213,7 +1232,7 @@
         <v>47</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="O12" s="1">
         <v>99001002</v>
@@ -1222,7 +1241,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1"/>
       <c r="C13" s="1">
         <v>10008</v>
       </c>
@@ -1230,7 +1250,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -1247,8 +1267,8 @@
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K13" t="s">
-        <v>83</v>
+      <c r="K13" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>56</v>
@@ -1257,7 +1277,7 @@
         <v>41</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O13" s="1">
         <v>99001003</v>
@@ -1266,7 +1286,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
       <c r="C14" s="1">
         <v>10009</v>
       </c>
@@ -1274,7 +1295,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -1291,8 +1312,8 @@
       <c r="J14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K14" t="s">
-        <v>84</v>
+      <c r="K14" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>51</v>
@@ -1301,7 +1322,7 @@
         <v>52</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="O14" s="1">
         <v>99001002</v>
@@ -1310,7 +1331,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
       <c r="C15" s="1">
         <v>10010</v>
       </c>
@@ -1318,7 +1340,7 @@
         <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -1335,8 +1357,8 @@
       <c r="J15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K15" t="s">
-        <v>85</v>
+      <c r="K15" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>56</v>
@@ -1345,7 +1367,7 @@
         <v>41</v>
       </c>
       <c r="N15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O15" s="1">
         <v>99001004</v>
@@ -1354,7 +1376,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
       <c r="C16" s="1">
         <v>10011</v>
       </c>
@@ -1362,7 +1385,7 @@
         <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -1379,8 +1402,8 @@
       <c r="J16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K16" t="s">
-        <v>83</v>
+      <c r="K16" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>56</v>
@@ -1389,7 +1412,7 @@
         <v>41</v>
       </c>
       <c r="N16" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O16" s="1">
         <v>99001002</v>
@@ -1398,7 +1421,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
       <c r="C17" s="1">
         <v>10012</v>
       </c>
@@ -1406,7 +1430,7 @@
         <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -1423,8 +1447,8 @@
       <c r="J17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K17" t="s">
-        <v>86</v>
+      <c r="K17" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>59</v>
@@ -1433,7 +1457,7 @@
         <v>61</v>
       </c>
       <c r="N17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="O17" s="1">
         <v>99001003</v>
@@ -1442,9 +1466,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/ZuoQiShowConfig.xlsx
+++ b/Excel/ZuoQiShowConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8CD93A-3E03-4C53-9AFA-2D18AA5D5636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DF54B6-F285-41D4-92A4-4F10A536FB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZuoQiShowProto" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>ID</t>
   </si>
@@ -366,6 +366,33 @@
   <si>
     <t>Ghost Dragon</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>魂角玄羊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dark Goat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过珍宝商人获得</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提升10%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack power increases by 10%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100402,0.1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obtained from the Treasure Merchant</t>
   </si>
 </sst>
 </file>
@@ -452,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -462,6 +489,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -766,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P20"/>
+  <dimension ref="B1:P30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -961,7 +991,7 @@
       <c r="M6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="5" t="s">
         <v>78</v>
       </c>
       <c r="O6" s="1">
@@ -1006,7 +1036,7 @@
       <c r="M7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="5" t="s">
         <v>79</v>
       </c>
       <c r="O7" s="1">
@@ -1051,7 +1081,7 @@
       <c r="M8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="5" t="s">
         <v>80</v>
       </c>
       <c r="O8" s="1">
@@ -1096,7 +1126,7 @@
       <c r="M9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="5" t="s">
         <v>81</v>
       </c>
       <c r="O9" s="1">
@@ -1141,7 +1171,7 @@
       <c r="M10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="5" t="s">
         <v>82</v>
       </c>
       <c r="O10" s="1">
@@ -1186,7 +1216,7 @@
       <c r="M11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="5" t="s">
         <v>83</v>
       </c>
       <c r="O11" s="1">
@@ -1231,7 +1261,7 @@
       <c r="M12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="5" t="s">
         <v>84</v>
       </c>
       <c r="O12" s="1">
@@ -1276,7 +1306,7 @@
       <c r="M13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="5" t="s">
         <v>82</v>
       </c>
       <c r="O13" s="1">
@@ -1321,7 +1351,7 @@
       <c r="M14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N14" t="s">
+      <c r="N14" s="5" t="s">
         <v>85</v>
       </c>
       <c r="O14" s="1">
@@ -1366,7 +1396,7 @@
       <c r="M15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="5" t="s">
         <v>82</v>
       </c>
       <c r="O15" s="1">
@@ -1411,7 +1441,7 @@
       <c r="M16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="5" t="s">
         <v>82</v>
       </c>
       <c r="O16" s="1">
@@ -1445,18 +1475,18 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N17" s="5" t="s">
         <v>86</v>
       </c>
       <c r="O17" s="1">
@@ -1466,9 +1496,63 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1">
+        <v>10013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>10013</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10013</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="O18" s="1">
+        <v>99001002</v>
+      </c>
+      <c r="P18" s="1">
+        <v>2</v>
+      </c>
+    </row>
     <row r="19" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
